--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_954_South_Africa_Indian_Ocean_Coast.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_954_South_Africa_Indian_Ocean_Coast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra082c214b7424d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0ba40fe61d8c403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R8e001d3084ea48b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R0f60b690acc2428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R32cd5ed2d8104fb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R817181438dfa40c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R493fa0256a7744ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rba49c8712f864d5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd67d284c334d40b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfbe8bdf7410045ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4312563669b84a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdd4cedd250d94199"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ954CommercialTable" displayName="EEZ954CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ954CommercialTable" displayName="EEZ954CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ954FunctionalTable" displayName="EEZ954FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ954FunctionalTable" displayName="EEZ954FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ954ValidationTable" displayName="EEZ954ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ954ValidationTable" displayName="EEZ954ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5652,7 +5606,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10035363b02c48f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1904a75d94944bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5662,20 +5616,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5683,552 +5627,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>78.8418654124</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.318543995432229</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2082.3033385823846</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>78.8418654124</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2091.450777279973</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$75,A2,'Species'!$U$2:$U$75))</x:f>
-        <x:v>164893.880698967</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.318543995432229</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2082.3033385823846</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>164172.67956830355</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>721.2011306634522</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.004392942434514</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0043929424345138905</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>578.5507981644</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5813648048927447</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>38.13860509922042</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>578.5507981644</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>54.23528328420727</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$75,A3,'Species'!$U$2:$U$75))</x:f>
-        <x:v>31377.86643275046</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5813648048927447</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>38.13860509922042</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>22065.12042103083</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>9312.746011719628</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4220573390953901</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.42205733909539017</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>52.692432431200004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.8400967367904046</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>69.19850897590841</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>52.692432431200004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>69.20873112480594</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$75,A4,'Species'!$U$2:$U$75))</x:f>
-        <x:v>3646.7763884429255</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.8400967367904046</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>69.19850897590841</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3646.237758552841</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0.538629890084394</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0001477220976116</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00014772209761169589</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>250.0175068415</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.23</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>16.982436524617444</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>250.0175068415</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>16.982436524617444</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$75,A5,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4245.906439978881</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.23</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>16.982436524617444</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>4245.906439978881</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1819.845159427</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.3563740239695243</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>227.18205514939845</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1819.845159427</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>261.77077986963826</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$75,A6,'Species'!$U$2:$U$75))</x:f>
-        <x:v>476382.286625192</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.3563740239695243</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>227.18205514939845</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>413436.1633723105</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>62946.12325288146</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1522511304754848</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1522511304754847</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6337.074794661</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6222318430935427</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>419.01719291130024</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6337.074794661</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>951.6596721206697</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$75,A7,'Species'!$U$2:$U$75))</x:f>
-        <x:v>6030738.521291248</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6222318430935427</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>419.01719291130024</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2655343.2917278064</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3375395.229563441</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>2.2711709405253977</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>1.2711709405253977</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>10.2411459366</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.9161994795253428</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>824.516743911865</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>10.2411459366</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>825.7839754812279</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$75,A8,'Species'!$U$2:$U$75))</x:f>
-        <x:v>8456.974205008972</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.9161994795253428</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>824.516743911865</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>8443.996301571658</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>12.977903437313216</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.001536938550636</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0015369385506359913</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1767.6796238786999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.39815006411004</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2501.209468769234</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1767.6796238786999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2554.7539060735935</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$75,A9,'Species'!$U$2:$U$75))</x:f>
-        <x:v>4515986.423790809</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.39815006411004</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2501.209468769234</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4421337.012995842</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>94649.41079496685</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.021407418280208</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.021407418280207872</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>845.8555090549</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.420037830693381</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2630.4971202864594</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>845.8555090549</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2693.3900504978756</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$75,A10,'Species'!$U$2:$U$75))</x:f>
-        <x:v>2278218.8122472833</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.420037830693381</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2630.4971202864594</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2225020.480747352</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>53198.3314999314</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0239091423922817</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.023909142392281646</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f20563847de4b58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc97eadafcd834166"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6238,20 +5823,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6259,1146 +5834,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>266.71750686219997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.7955989955620555</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>624.5957079642545</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>266.71750686219997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>629.0326627997259</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$75,A2,'Species'!$U$2:$U$75))</x:f>
-        <x:v>167774.02355683382</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.7955989955620555</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>624.5957079642545</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>166590.6100250567</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1183.4135317771288</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0071037229025042</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.007103722902504127</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>5.4331037568</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>5.4331037568</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.622776601683796</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$75,A3,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>171.80982635505535</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>171.80982635505535</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>47.1418654124</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.351186841482969</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2244.8474907914165</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>47.1418654124</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2245.683694114228</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$75,A4,'Species'!$U$2:$U$75))</x:f>
-        <x:v>105865.71846675417</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.351186841482969</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2244.8474907914165</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>105826.29828225281</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>39.42018450135947</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0003724989453588</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0003724989453587481</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>361.72426992799996</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.133910886705155</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1361.165355004658</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>361.72426992799996</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1418.6614602363436</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$75,A5,'Species'!$U$2:$U$75))</x:f>
-        <x:v>513164.28097898175</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.133910886705155</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1361.165355004658</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>492366.5442903468</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>20797.736688634963</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0422403531064666</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04224035310646657</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3.7199999999999998</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.56</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>363.0780547701014</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3.7199999999999998</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>363.0780547701014</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$75,A6,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1350.6503637447772</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.56</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>363.0780547701014</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>1350.6503637447772</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1813.6491282177</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.484980735762489</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>3054.7856074167157</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1813.6491282177</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>3104.5981618232418</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$75,A7,'Species'!$U$2:$U$75))</x:f>
-        <x:v>5630651.749656997</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.484980735762489</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>3054.7856074167157</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>5540309.253783304</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>90342.49587369245</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0163063994689467</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01630639946894668</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3.0944374289</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3.0944374289</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$75,A8,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1260.612779432726</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>1260.612779432726</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>10.020000000000001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>10.020000000000001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$75,A9,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8334.272986448763</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>8334.272986448763</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1764.4746134819</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.3995697616600475</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2509.3992373085052</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1764.4746134819</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2558.6404075693945</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$75,A10,'Species'!$U$2:$U$75))</x:f>
-        <x:v>4514656.044185178</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.3995697616600475</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2509.3992373085052</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>4427771.249321699</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>86884.79486347921</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.01962269276598</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.01962269276598002</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>340.3673328858</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.692734443552003</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>49.287233696249665</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>340.3673328858</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>58.730380069380445</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$75,A11,'Species'!$U$2:$U$75))</x:f>
-        <x:v>19989.90282358437</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.692734443552003</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>49.287233696249665</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>16775.76427851163</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>3214.1385450727394</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1915941647552706</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.19159416475527055</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>31.7221145943</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.270153369685729</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1862.7448428138232</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>31.7221145943</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1862.943363573524</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$75,A12,'Species'!$U$2:$U$75))</x:f>
-        <x:v>59096.50286197002</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.270153369685729</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1862.7448428138232</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>59090.20536368144</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>6.297498288578936</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0001065743171786</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.00010657431717862267</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1142.0783699195</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.3144470189977597</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>206.27520101061785</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1142.0783699195</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>215.9846531502136</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$75,A13,'Species'!$U$2:$U$75))</x:f>
-        <x:v>246671.40059742454</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.3144470189977597</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>206.27520101061785</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>235582.4453250236</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>11088.955272400926</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.047070380210639</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.04707038021063896</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>3639.8113846265</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4443388375425417</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>278.188285262045</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>3639.8113846265</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>308.7011824073536</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$75,A14,'Species'!$U$2:$U$75))</x:f>
-        <x:v>1123614.0781739475</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4443388375425417</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>278.188285262045</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1012552.8877665157</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>111061.1904074318</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1096843352572032</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.10968433525720324</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>459.43414232609996</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.083134037297214</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1210.9718208786132</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>459.43414232609996</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1609.578097932498</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$75,A15,'Species'!$U$2:$U$75))</x:f>
-        <x:v>739495.1329304925</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.083134037297214</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1210.9718208786132</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>556361.7999064412</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>183133.33302405127</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3291623059937747</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.3291623059937747</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>1362.7466116071002</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.996637593692325</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>99.22876671979951</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>1362.7466116071002</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>268.6385978370945</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$75,A16,'Species'!$U$2:$U$75))</x:f>
-        <x:v>366086.338949383</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.996637593692325</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>99.22876671979951</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>135223.66562135817</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>230862.67332802483</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.7072653094205186</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.7072653094205188</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>250.0175068415</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.23</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>16.982436524617444</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>250.0175068415</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>16.982436524617444</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$75,A17,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4245.906439978881</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.23</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>16.982436524617444</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>4245.906439978881</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>238.1834652786</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.4222161132295</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>26.437239976085074</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>238.1834652786</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>47.81173032244595</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$75,A18,'Species'!$U$2:$U$75))</x:f>
-        <x:v>11387.963609166092</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.4222161132295</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>26.437239976085074</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>6296.913429905875</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>5091.050179260217</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.8084993125491193</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.8084993125491193</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>0.3399772413</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>0.3399772413</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$75,A19,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>59.081273168706666</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>59.081273168706666</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>0.0124324312</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>177.82794100389228</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>0.0124324312</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>177.82794100389225</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$75,A20,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>2.2108336419685495</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.25</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>177.82794100389228</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>2.2108336419685495</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.1105729679</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.1105729679</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$75,A21,'Species'!$U$2:$U$75))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>69.76682619747763</x:v>
       </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>69.76682619747763</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R108f74dfa65b4ae0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5dfdd8be9de44aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7573,7 +6404,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7672,7 +6503,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>13513947.448119681</x:v>
+        <x:v>9917710.889332749</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7686,7 +6517,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>13513947.448119681</x:v>
+        <x:v>12770241.948723067</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7700,7 +6531,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-3596236.5587869324</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7714,7 +6545,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-743705.4993966147</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7725,9 +6556,9 @@
         <x:v>EEZ_954</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7739,47 +6570,19 @@
         <x:v>EEZ_954</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_954</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_954</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58ef255735dc48b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10da115baf584d46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7826,7 +6629,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
